--- a/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
+++ b/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
@@ -505,7 +505,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>55 preguntas · 191 opciones · 63 campos de caso · 12 rangos · 1 pares de consistencia.</t>
+          <t>55 preguntas · 191 opciones · 84 campos de caso · 12 rangos · 1 pares de consistencia.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I8" s="7" t="n"/>
     </row>
@@ -1224,9 +1224,13 @@
       </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" s="7" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Mismo detector de apagaincendios que D22: aplicar idéntica fórmula de índice.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2108,9 +2112,13 @@
       </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I53" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Solo cuentan las iniciativas implementadas.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -5912,7 +5920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6047,7 +6055,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Nombre (texto ≤ 40 car.)</t>
+          <t>Indicador 1 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -6060,7 +6068,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cómo se calculaba (texto ≤ 40 car.)</t>
+          <t>Indicador 1 · Cómo se calculaba (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -6073,7 +6081,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia (diaria / semanal / mensual)</t>
+          <t>Indicador 1 · Frecuencia (diaria / semanal / mensual)</t>
         </is>
       </c>
       <c r="C13" s="7" t="n"/>
@@ -6086,7 +6094,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>A quién lo reportabas (lista)</t>
+          <t>Indicador 1 · A quién lo reportabas (lista)</t>
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
@@ -6094,12 +6102,12 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Qué se estaba desviando (texto ≤ 60 car.)</t>
+          <t>Indicador 2 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -6107,12 +6115,12 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>¿Cómo lo detectaste? (revisión programada / un dato del reporte / recorrido en terreno / me lo avisó alguien del equipo / por casualidad)</t>
+          <t>Indicador 2 · Cómo se calculaba (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C16" s="7" t="n"/>
@@ -6120,12 +6128,12 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Días de anticipación ___</t>
+          <t>Indicador 2 · Frecuencia (diaria / semanal / mensual)</t>
         </is>
       </c>
       <c r="C17" s="7" t="n"/>
@@ -6133,12 +6141,12 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Qué hiciste (lista de 6)</t>
+          <t>Indicador 2 · A quién lo reportabas (lista)</t>
         </is>
       </c>
       <c r="C18" s="7" t="n"/>
@@ -6146,12 +6154,12 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>¿Se evitó el impacto? (sí completamente / en parte / no)</t>
+          <t>Indicador 3 · Nombre (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C19" s="7" t="n"/>
@@ -6159,12 +6167,12 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Qué pasó (texto ≤ 60 car.)</t>
+          <t>Indicador 3 · Cómo se calculaba (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C20" s="7" t="n"/>
@@ -6172,12 +6180,12 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>¿Cuándo te enteraste? (el mismo día / esa semana / al cierre / cuando ya reclamaron)</t>
+          <t>Indicador 3 · Frecuencia (diaria / semanal / mensual)</t>
         </is>
       </c>
       <c r="C21" s="7" t="n"/>
@@ -6185,12 +6193,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>¿Qué cambiaste en tu forma de controlar? (nada / hablé con el responsable / agregué un punto de revisión / cambié la frecuencia / cambié el formato de control / cambié a la persona)</t>
+          <t>Indicador 3 · A quién lo reportabas (lista)</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -6198,12 +6206,12 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>¿Volvió a pasar? (sí / no / no lo sé) Campo 3 = "nada", "hablé con el responsable" o "cambié a la persona" → ítem puntúa 0.</t>
+          <t>Qué se estaba desviando (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
@@ -6211,12 +6219,12 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Qué estaba fallando (texto ≤ 60 car.)</t>
+          <t>¿Cómo lo detectaste? (revisión programada / un dato del reporte / recorrido en terreno / me lo avisó alguien del equipo / por casualidad)</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
@@ -6224,12 +6232,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Qué hiciste (lista de 7)</t>
+          <t>Días de anticipación ___</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
@@ -6237,12 +6245,12 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia de seguimiento (lista)</t>
+          <t>Qué hiciste (lista de 6)</t>
         </is>
       </c>
       <c r="C26" s="7" t="n"/>
@@ -6250,12 +6258,12 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Semanas que tomó ___</t>
+          <t>¿Se evitó el impacto? (sí completamente / en parte / no)</t>
         </is>
       </c>
       <c r="C27" s="7" t="n"/>
@@ -6263,12 +6271,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>¿Se sostuvo después? (sí / volvió a caer / se fue de la empresa)</t>
+          <t>Qué pasó (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C28" s="7" t="n"/>
@@ -6276,12 +6284,12 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Con quién (mi equipo / mi jefe / otras áreas / cliente)</t>
+          <t>¿Cuándo te enteraste? (el mismo día / esa semana / al cierre / cuando ya reclamaron)</t>
         </is>
       </c>
       <c r="C29" s="7" t="n"/>
@@ -6289,12 +6297,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia (diaria / semanal / quincenal / mensual)</t>
+          <t>¿Qué cambiaste en tu forma de controlar? (nada / hablé con el responsable / agregué un punto de revisión / cambié la frecuencia / cambié el formato de control / cambié a la persona)</t>
         </is>
       </c>
       <c r="C30" s="7" t="n"/>
@@ -6302,12 +6310,12 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>¿Agenda previa? (sí/no)</t>
+          <t>¿Volvió a pasar? (sí / no / no lo sé) Campo 3 = "nada", "hablé con el responsable" o "cambié a la persona" → ítem puntúa 0.</t>
         </is>
       </c>
       <c r="C31" s="7" t="n"/>
@@ -6315,12 +6323,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>¿Qué quedaba registrado? (nada / mis notas / acta con acuerdos / registro en sistema)</t>
+          <t>Qué estaba fallando (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C32" s="7" t="n"/>
@@ -6328,12 +6336,12 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Descripción (texto ≤ 60 car.)</t>
+          <t>Qué hiciste (lista de 7)</t>
         </is>
       </c>
       <c r="C33" s="7" t="n"/>
@@ -6341,12 +6349,12 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>¿Era previsible? (sí, no lo previne / sí, falló la prevención / no, imprevisible)</t>
+          <t>Frecuencia de seguimiento (lista)</t>
         </is>
       </c>
       <c r="C34" s="7" t="n"/>
@@ -6354,12 +6362,12 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Origen (falla de persona / falla de proceso / externo / otra área / falta de información a tiempo)</t>
+          <t>Semanas que tomó ___</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -6367,12 +6375,12 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Frecuencia con que ocurre (primera vez / antes este año / todos los meses / todas las semanas)</t>
+          <t>¿Se sostuvo después? (sí / volvió a caer / se fue de la empresa)</t>
         </is>
       </c>
       <c r="C36" s="7" t="n"/>
@@ -6380,12 +6388,12 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Qué dejaste hecho (nada / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé) Mismo detector de apagaincendios que D22. Aplicar idéntica fórmula de índice.</t>
+          <t>Con quién (mi equipo / mi jefe / otras áreas / cliente)</t>
         </is>
       </c>
       <c r="C37" s="7" t="n"/>
@@ -6393,12 +6401,12 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Indicador (texto ≤ 40 car.)</t>
+          <t>Frecuencia (diaria / semanal / quincenal / mensual)</t>
         </is>
       </c>
       <c r="C38" s="7" t="n"/>
@@ -6406,12 +6414,12 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Antes ___</t>
+          <t>¿Agenda previa? (sí/no)</t>
         </is>
       </c>
       <c r="C39" s="7" t="n"/>
@@ -6419,12 +6427,12 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Después ___</t>
+          <t>¿Qué quedaba registrado? (nada / mis notas / acta con acuerdos / registro en sistema)</t>
         </is>
       </c>
       <c r="C40" s="7" t="n"/>
@@ -6432,12 +6440,12 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Unidad (lista)</t>
+          <t>Problema 1 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C41" s="7" t="n"/>
@@ -6445,12 +6453,12 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Meses que tomó ___</t>
+          <t>Problema 1 · ¿Era previsible? (sí, no lo previne / sí, falló la prevención / no, imprevisible)</t>
         </is>
       </c>
       <c r="C42" s="7" t="n"/>
@@ -6458,12 +6466,12 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Quién puede confirmarlo (nombre + cargo + contacto)</t>
+          <t>Problema 1 · Origen (falla de persona / falla de proceso / externo / otra área / falta de información a tiempo)</t>
         </is>
       </c>
       <c r="C43" s="7" t="n"/>
@@ -6471,12 +6479,12 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Qué faltó (personal / tiempo / materiales / equipos / información)</t>
+          <t>Problema 1 · Frecuencia con que ocurre (primera vez / antes este año / todos los meses / todas las semanas)</t>
         </is>
       </c>
       <c r="C44" s="7" t="n"/>
@@ -6484,12 +6492,12 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Qué hiciste (lista de 7)</t>
+          <t>Problema 1 · Qué dejaste hecho (nada / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé) Mismo detector de apagaincendios que D22. Aplicar idéntica fórmula de índice.</t>
         </is>
       </c>
       <c r="C45" s="7" t="n"/>
@@ -6497,12 +6505,12 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>¿Cumpliste al 100%? (sí / en parte / se cumplió con menor calidad)</t>
+          <t>Problema 2 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C46" s="7" t="n"/>
@@ -6510,12 +6518,12 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>¿Qué te costó? (horas extra mías / horas extra del equipo / calidad / nada, se reorganizó)</t>
+          <t>Problema 2 · ¿Era previsible? (sí, no lo previne / sí, falló la prevención / no, imprevisible)</t>
         </is>
       </c>
       <c r="C47" s="7" t="n"/>
@@ -6523,12 +6531,12 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Qué mejoraste (texto ≤ 60 car.)</t>
+          <t>Problema 2 · Origen (falla de persona / falla de proceso / externo / otra área / falta de información a tiempo)</t>
         </is>
       </c>
       <c r="C48" s="7" t="n"/>
@@ -6536,12 +6544,12 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>¿Te lo pidieron o fue tuyo? (me lo pidieron / fue idea mía)</t>
+          <t>Problema 2 · Frecuencia con que ocurre (primera vez / antes este año / todos los meses / todas las semanas)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n"/>
@@ -6549,12 +6557,12 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Qué mejoró (indicador + antes + después)</t>
+          <t>Problema 2 · Qué dejaste hecho (nada / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé) Mismo detector de apagaincendios que D22. Aplicar idéntica fórmula de índice.</t>
         </is>
       </c>
       <c r="C50" s="7" t="n"/>
@@ -6562,12 +6570,12 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>¿Sigue aplicándose? (sí / no / no lo sé)</t>
+          <t>Problema 3 · Descripción (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C51" s="7" t="n"/>
@@ -6575,12 +6583,12 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Hora en que despiertas ___</t>
+          <t>Problema 3 · ¿Era previsible? (sí, no lo previne / sí, falló la prevención / no, imprevisible)</t>
         </is>
       </c>
       <c r="C52" s="7" t="n"/>
@@ -6588,12 +6596,12 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Hora de entrada ___</t>
+          <t>Problema 3 · Origen (falla de persona / falla de proceso / externo / otra área / falta de información a tiempo)</t>
         </is>
       </c>
       <c r="C53" s="7" t="n"/>
@@ -6601,12 +6609,12 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Hora de salida real ___</t>
+          <t>Problema 3 · Frecuencia con que ocurre (primera vez / antes este año / todos los meses / todas las semanas)</t>
         </is>
       </c>
       <c r="C54" s="7" t="n"/>
@@ -6614,12 +6622,12 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Hora en que duermes ___</t>
+          <t>Problema 3 · Qué dejaste hecho (nada / avisé a quien corresponde / cambié el procedimiento / agregué un punto de control / lo escalé) Mismo detector de apagaincendios que D22. Aplicar idéntica fórmula de índice.</t>
         </is>
       </c>
       <c r="C55" s="7" t="n"/>
@@ -6627,12 +6635,12 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>¿Revisas trabajo después de salir? (nunca / a veces / todos los días)</t>
+          <t>Indicador (texto ≤ 40 car.)</t>
         </is>
       </c>
       <c r="C56" s="7" t="n"/>
@@ -6640,12 +6648,12 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Qué hiciste (texto ≤ 60 car.)</t>
+          <t>Antes ___</t>
         </is>
       </c>
       <c r="C57" s="7" t="n"/>
@@ -6653,12 +6661,12 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Cuándo (esta semana / este mes / este año / no recuerdo)</t>
+          <t>Después ___</t>
         </is>
       </c>
       <c r="C58" s="7" t="n"/>
@@ -6666,12 +6674,12 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Tiempo que te tomó (lista)</t>
+          <t>Unidad (lista)</t>
         </is>
       </c>
       <c r="C59" s="7" t="n"/>
@@ -6679,12 +6687,12 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>¿Alguien se enteró? (sí / no)</t>
+          <t>Meses que tomó ___</t>
         </is>
       </c>
       <c r="C60" s="7" t="n"/>
@@ -6692,12 +6700,12 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Qué exigías (texto ≤ 60 car.)</t>
+          <t>Quién puede confirmarlo (nombre + cargo + contacto)</t>
         </is>
       </c>
       <c r="C61" s="7" t="n"/>
@@ -6705,12 +6713,12 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Cómo lo verificabas (a criterio / checklist / medición con número / revisión de un tercero)</t>
+          <t>Qué faltó (personal / tiempo / materiales / equipos / información)</t>
         </is>
       </c>
       <c r="C62" s="7" t="n"/>
@@ -6718,12 +6726,12 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Qué pasaba si no se cumplía (nada / se corregía / no se entregaba hasta cumplir / consecuencia formal)</t>
+          <t>Qué hiciste (lista de 7)</t>
         </is>
       </c>
       <c r="C63" s="7" t="n"/>
@@ -6731,12 +6739,12 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>% de cumplimiento alcanzado ___</t>
+          <t>¿Cumpliste al 100%? (sí / en parte / se cumplió con menor calidad)</t>
         </is>
       </c>
       <c r="C64" s="7" t="n"/>
@@ -6744,12 +6752,12 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Qué era (texto ≤ 40 car.)</t>
+          <t>¿Qué te costó? (horas extra mías / horas extra del equipo / calidad / nada, se reorganizó)</t>
         </is>
       </c>
       <c r="C65" s="7" t="n"/>
@@ -6757,12 +6765,12 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>¿Se implementó? (sí / parcial / no)</t>
+          <t>Qué mejoraste (texto ≤ 60 car.)</t>
         </is>
       </c>
       <c r="C66" s="7" t="n"/>
@@ -6770,15 +6778,288 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>¿Te lo pidieron o fue tuyo? (me lo pidieron / fue idea mía)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Qué mejoró (indicador + antes + después)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>¿Sigue aplicándose? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que despiertas ___</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Hora de entrada ___</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Hora de salida real ___</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Hora en que duermes ___</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>¿Revisas trabajo después de salir? (nunca / a veces / todos los días)</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>C46</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Qué hiciste (texto ≤ 60 car.)</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>C46</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Cuándo (esta semana / este mes / este año / no recuerdo)</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>C46</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Tiempo que te tomó (lista)</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>C46</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>¿Alguien se enteró? (sí / no)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Qué exigías (texto ≤ 60 car.)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Cómo lo verificabas (a criterio / checklist / medición con número / revisión de un tercero)</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Qué pasaba si no se cumplía (nada / se corregía / no se entregaba hasta cumplir / consecuencia formal)</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>% de cumplimiento alcanzado ___</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
           <t>C49</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>¿Sigue viva? (sí / no / no lo sé) Solo cuentan las implementadas.</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="n"/>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · Qué era (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · ¿Se implementó? (sí / parcial / no)</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 1 · ¿Sigue viva? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · Qué era (texto ≤ 40 car.)</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · ¿Se implementó? (sí / parcial / no)</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Iniciativa 2 · ¿Sigue viva? (sí / no / no lo sé)</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
+++ b/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Revisar si la instrucción y los recursos estaban dados antes de reclamar Opción Clave</t>
+          <t>Revisar si la instrucción y los recursos estaban dados antes de reclamar</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Me los reporta el responsable el mismo día Opción Valor</t>
+          <t>Me los reporta el responsable el mismo día</t>
         </is>
       </c>
       <c r="C78" s="7" t="n"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Lo que más caro sale si no se hace Opción Valor</t>
+          <t>Lo que más caro sale si no se hace</t>
         </is>
       </c>
       <c r="C101" s="7" t="n"/>

--- a/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
+++ b/docs/insumos/banco-v3-coordinacion-y-supervision.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,8 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,6 +571,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -615,6 +618,16 @@
           <t>Nota interna (opcional)</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Fórmula de puntaje (solo V)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Usa los rangos de (solo V)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -660,6 +673,16 @@
       <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Guía para el evaluador. El candidato nunca la ve.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V no se puntúa por tramos: la fórmula, en palabras.</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Si el ítem V usa la tabla de otra pregunta: su código.</t>
         </is>
       </c>
     </row>
@@ -1732,6 +1755,11 @@
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n"/>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>D57</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -2264,6 +2292,11 @@
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
